--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Dealer people" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Architect firms" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Architect people" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Clients" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="People (no company)" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Products &amp; warehouses" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Lists" sheetId="8" state="hidden" r:id="rId8"/>
   </sheets>
@@ -549,7 +549,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Companies first, then the people who work in them, then the clients. A person's company is written exactly as its name on the companies sheet.</t>
+          <t>Companies first, then the people who work in them, then people with no company. A person's company is written exactly as its name on the companies sheet.</t>
         </is>
       </c>
     </row>
@@ -716,12 +716,12 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Clients</t>
+          <t>People (no company)</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Clients who are not under any dealer or architect: an individual, or a firm on its own (builder, hotel, corporate). One row each.</t>
+          <t>People with no company: an individual, or a firm on its own (builder, hotel, corporate). Not a dealer's or an architect's staff: they go on the people sheets. One row each.</t>
         </is>
       </c>
     </row>
@@ -10954,7 +10954,7 @@
   <dimension ref="A1:Q201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="29" customWidth="1" min="4" max="4"/>
@@ -10976,7 +10976,7 @@
     <row r="1" ht="48" customHeight="1">
       <c r="A1" s="5" t="inlineStr">
         <is>
-          <t>Client name (person or firm) *</t>
+          <t>Person or firm name *</t>
         </is>
       </c>
       <c r="B1" s="5" t="inlineStr">

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -7153,34 +7153,34 @@
   </sheetData>
   <dataValidations count="10">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$A$1:$A$3</formula1>
+      <formula1>=Lists!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$B$1:$B$16</formula1>
+      <formula1>=Lists!$B$2:$B$17</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$C$1:$C$22</formula1>
+      <formula1>=Lists!$C$2:$C$23</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type several separated by commas." type="list">
-      <formula1>=Lists!$D$1:$D$22</formula1>
+      <formula1>=Lists!$D$2:$D$23</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$E$1:$E$2</formula1>
+      <formula1>=Lists!$E$2:$E$3</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$F$1:$F$4</formula1>
+      <formula1>=Lists!$F$2:$F$5</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
       <formula1>='Dealer companies'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$G$1:$G$13</formula1>
+      <formula1>=Lists!$G$2:$G$14</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$H$1:$H$3</formula1>
+      <formula1>=Lists!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$I$1:$I$2</formula1>
+      <formula1>=Lists!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12572,10 +12572,10 @@
       <formula1>='Dealer companies'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$J$1:$J$16</formula1>
+      <formula1>=Lists!$J$2:$J$17</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$K$1:$K$2</formula1>
+      <formula1>=Lists!$K$2:$K$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18837,31 +18837,31 @@
   </sheetData>
   <dataValidations count="9">
     <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$L$1:$L$2</formula1>
+      <formula1>=Lists!$L$2:$L$3</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$M$1:$M$16</formula1>
+      <formula1>=Lists!$M$2:$M$17</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$N$1:$N$22</formula1>
+      <formula1>=Lists!$N$2:$N$23</formula1>
     </dataValidation>
     <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type several separated by commas." type="list">
-      <formula1>=Lists!$O$1:$O$22</formula1>
+      <formula1>=Lists!$O$2:$O$23</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$P$1:$P$2</formula1>
+      <formula1>=Lists!$P$2:$P$3</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$Q$1:$Q$3</formula1>
+      <formula1>=Lists!$Q$2:$Q$4</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$R$1:$R$13</formula1>
+      <formula1>=Lists!$R$2:$R$14</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$S$1:$S$3</formula1>
+      <formula1>=Lists!$S$2:$S$4</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$T$1:$T$2</formula1>
+      <formula1>=Lists!$T$2:$T$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24253,10 +24253,10 @@
       <formula1>='Architect firms'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$U$1:$U$16</formula1>
+      <formula1>=Lists!$U$2:$U$17</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$V$1:$V$2</formula1>
+      <formula1>=Lists!$V$2:$V$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29909,19 +29909,19 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="B2:B1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$W$1:$W$9</formula1>
+      <formula1>=Lists!$W$2:$W$10</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$X$1:$X$22</formula1>
+      <formula1>=Lists!$X$2:$X$23</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$Y$1:$Y$2</formula1>
+      <formula1>=Lists!$Y$2:$Y$3</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$Z$1:$Z$13</formula1>
+      <formula1>=Lists!$Z$2:$Z$14</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$AA$1:$AA$3</formula1>
+      <formula1>=Lists!$AA$2:$AA$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29934,1333 +29934,1470 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA22"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Distributor</t>
+          <t>-</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>@roles</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>@cities</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>@cities</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>@team</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Platinum</t>
+          <t>@dealer_grades</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>@sources</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>@client_statuses</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>@roles</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>-</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Design firm</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>@roles</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>@cities</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>@cities</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>@team</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>@architect_ratings</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>@sources</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>@client_statuses</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>EGO direct</t>
+          <t>@relationships</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>@roles</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>-</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Individual</t>
+          <t>@client_types</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Mumbai</t>
+          <t>@cities</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>@team</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Meta Ads</t>
+          <t>@sources</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>Active</t>
+          <t>@client_statuses</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Dealer</t>
+          <t>Distributor</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ZippyScale Admin</t>
+          <t>Roshan Bisani</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Platinum</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Meta Ads</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Active</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Design firm</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Roshan Bisani</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Google Ads</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Prospect</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Architect</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Partner</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Navi Mumbai</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Navi Mumbai</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>ZippyScale Admin</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Active</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Via dealer</t>
+          <t>EGO direct</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>Partner</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Homeowner</t>
+          <t>Individual</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Navi Mumbai</t>
+          <t>Mumbai</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>ZippyScale Admin</t>
+          <t>Roshan Bisani</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>Google Ads</t>
+          <t>Meta Ads</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Dealer</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Architect</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Via dealer</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Partner</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Homeowner</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Navi Mumbai</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Google Ads</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Prospect</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Sub-dealer</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>Inactive</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Director</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Builder</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Thane</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Website</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Inactive</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Principal</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Contractor</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Pune</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Pune</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>C</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>IndiaMART</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>IndiaMART</t>
+          <t>WhatsApp</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>Purchase</t>
+          <t>Principal</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Contractor</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Nashik</t>
+          <t>Pune</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>IndiaMART</t>
+          <t>WhatsApp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Purchase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>JustDial</t>
+          <t>IndiaMART</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Purchase</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Purchase</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>JustDial</t>
+          <t>IndiaMART</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>Accounts</t>
+          <t>Purchase</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Corporate</t>
+          <t>Hotel</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Nagpur</t>
+          <t>Nashik</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>JustDial</t>
+          <t>IndiaMART</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Store manager</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>JustDial</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Store manager</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Store manager</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>JustDial</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>Store manager</t>
+          <t>Accounts</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Retail chain</t>
+          <t>Corporate</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>Ahmedabad</t>
+          <t>Nagpur</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>JustDial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Store manager</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>QR code</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Store manager</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Store manager</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>QR code</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sales</t>
+          <t>Store manager</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Institution</t>
+          <t>Retail chain</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Surat</t>
+          <t>Ahmedabad</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>QR code</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Telecaller</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Telecaller</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Telecaller</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>Telecaller</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Other firm</t>
+          <t>Institution</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Vadodara</t>
+          <t>Surat</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Walk-in</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Telecaller</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Telecaller</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Telecaller</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Telecaller</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Other firm</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Vadodara</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Site engineer</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field visit</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Site engineer</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Site engineer</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field visit</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>Site engineer</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Bengaluru</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field visit</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Project manager</t>
+          <t>Site engineer</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Project manager</t>
+          <t>Site engineer</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Project manager</t>
+          <t>Site engineer</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>Project manager</t>
+          <t>Site engineer</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Chennai</t>
+          <t>Bengaluru</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Senior architect</t>
+          <t>Project manager</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Senior architect</t>
+          <t>Project manager</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Senior architect</t>
+          <t>Project manager</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>Senior architect</t>
+          <t>Project manager</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Chennai</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior architect</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior architect</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior architect</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Senior architect</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Kochi</t>
+          <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Kochi</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>Interior designer</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>New Delhi</t>
+          <t>Kochi</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Interior designer</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Gurugram</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>Gurugram</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Noida</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>Noida</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Noida</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Jaipur</t>
+          <t>Noida</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Jaipur</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Chandigarh</t>
+          <t>Jaipur</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chandigarh</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Lucknow</t>
+          <t>Chandigarh</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Lucknow</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>Kolkata</t>
+          <t>Lucknow</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Kolkata</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
           <t>Indore</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>Indore</t>
         </is>

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -489,7 +489,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>EGO-WS-2</t>
+          <t>EGO-WS-3</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="20" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="36" customWidth="1" min="14" max="14"/>
     <col width="35" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="16" customWidth="1" min="17" max="17"/>
@@ -840,7 +840,7 @@
       </c>
       <c r="N1" s="5" t="inlineStr">
         <is>
-          <t>Areas they cover</t>
+          <t>Areas they cover (a distributor: its assigned area)</t>
         </is>
       </c>
       <c r="O1" s="5" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="R1" s="5" t="inlineStr">
         <is>
-          <t>Buys through (pick their distributor or dealer)</t>
+          <t>Distributor who serves them (sub-dealers only: pick the distributor)</t>
         </is>
       </c>
       <c r="S1" s="5" t="inlineStr">
@@ -7174,7 +7174,7 @@
       <formula1>='Dealer companies'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$G$2:$G$14</formula1>
+      <formula1>=Lists!$G$2:$G$16</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$H$2:$H$4</formula1>
@@ -18855,7 +18855,7 @@
       <formula1>=Lists!$Q$2:$Q$4</formula1>
     </dataValidation>
     <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$R$2:$R$14</formula1>
+      <formula1>=Lists!$R$2:$R$16</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$S$2:$S$4</formula1>
@@ -29918,7 +29918,7 @@
       <formula1>=Lists!$Y$2:$Y$3</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$Z$2:$Z$14</formula1>
+      <formula1>=Lists!$Z$2:$Z$16</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$AA$2:$AA$4</formula1>
@@ -30669,7 +30669,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>Runo</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -30694,7 +30694,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>Runo</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>QR code</t>
+          <t>Runo</t>
         </is>
       </c>
     </row>
@@ -30736,7 +30736,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>Sales Diary</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -30761,7 +30761,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>Sales Diary</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -30781,7 +30781,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Walk-in</t>
+          <t>Sales Diary</t>
         </is>
       </c>
     </row>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>QR code</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -30828,7 +30828,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>QR code</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -30848,7 +30848,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>QR code</t>
         </is>
       </c>
     </row>
@@ -30870,7 +30870,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -30895,7 +30895,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Walk-in</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -30910,7 +30910,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Field visit</t>
+          <t>Walk-in</t>
         </is>
       </c>
     </row>
@@ -30932,7 +30932,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -30957,7 +30957,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -30972,7 +30972,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Referral</t>
         </is>
       </c>
     </row>
@@ -30994,7 +30994,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Field visit</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -31019,7 +31019,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Field visit</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -31034,7 +31034,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Field visit</t>
         </is>
       </c>
     </row>
@@ -31056,7 +31056,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -31081,7 +31081,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Architect</t>
         </is>
       </c>
     </row>
@@ -31116,6 +31116,11 @@
           <t>Kochi</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Existing relationship</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Architect</t>
@@ -31136,6 +31141,11 @@
           <t>Kochi</t>
         </is>
       </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Existing relationship</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>Architect</t>
@@ -31144,6 +31154,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Existing relationship</t>
         </is>
       </c>
     </row>
@@ -31163,6 +31178,11 @@
           <t>New Delhi</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>Interior designer</t>
@@ -31183,6 +31203,11 @@
           <t>New Delhi</t>
         </is>
       </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>Interior designer</t>
@@ -31191,6 +31216,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -7165,7 +7165,7 @@
       <formula1>=Lists!$D$2:$D$23</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$E$2:$E$3</formula1>
+      <formula1>=Lists!$E$2:$E$28</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$F$2:$F$5</formula1>
@@ -18849,7 +18849,7 @@
       <formula1>=Lists!$O$2:$O$23</formula1>
     </dataValidation>
     <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$P$2:$P$3</formula1>
+      <formula1>=Lists!$P$2:$P$28</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$Q$2:$Q$4</formula1>
@@ -29915,7 +29915,7 @@
       <formula1>=Lists!$X$2:$X$23</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
-      <formula1>=Lists!$Y$2:$Y$3</formula1>
+      <formula1>=Lists!$Y$2:$Y$28</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$Z$2:$Z$16</formula1>
@@ -29934,7 +29934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30097,7 +30097,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>Aliza Arif Mukri</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -30152,7 +30152,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>Aliza Arif Mukri</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -30197,7 +30197,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>Roshan Bisani</t>
+          <t>Aliza Arif Mukri</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -30234,7 +30234,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZippyScale Admin</t>
+          <t>Anjali Maurya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -30289,7 +30289,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>ZippyScale Admin</t>
+          <t>Anjali Maurya</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -30334,7 +30334,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ZippyScale Admin</t>
+          <t>Anjali Maurya</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -30369,6 +30369,11 @@
           <t>Thane</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Basanti Damai</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>B</t>
@@ -30404,6 +30409,11 @@
           <t>Thane</t>
         </is>
       </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Basanti Damai</t>
+        </is>
+      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>C</t>
@@ -30432,6 +30442,11 @@
       <c r="X4" t="inlineStr">
         <is>
           <t>Thane</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Basanti Damai</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -30461,6 +30476,11 @@
           <t>Pune</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Bharti Kapoor</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>C</t>
@@ -30491,6 +30511,11 @@
           <t>Pune</t>
         </is>
       </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bharti Kapoor</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>WhatsApp</t>
@@ -30509,6 +30534,11 @@
       <c r="X5" t="inlineStr">
         <is>
           <t>Pune</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Bharti Kapoor</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -30533,6 +30563,11 @@
           <t>Nashik</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Dattatray Sudam Gadhave</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
           <t>IndiaMART</t>
@@ -30558,6 +30593,11 @@
           <t>Nashik</t>
         </is>
       </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dattatray Sudam Gadhave</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>IndiaMART</t>
@@ -30576,6 +30616,11 @@
       <c r="X6" t="inlineStr">
         <is>
           <t>Nashik</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Dattatray Sudam Gadhave</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -30600,6 +30645,11 @@
           <t>Nagpur</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Hardeep Kaur</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>JustDial</t>
@@ -30625,6 +30675,11 @@
           <t>Nagpur</t>
         </is>
       </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hardeep Kaur</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>JustDial</t>
@@ -30643,6 +30698,11 @@
       <c r="X7" t="inlineStr">
         <is>
           <t>Nagpur</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Hardeep Kaur</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -30667,6 +30727,11 @@
           <t>Ahmedabad</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Joycee Ashok Rokade</t>
+        </is>
+      </c>
       <c r="G8" t="inlineStr">
         <is>
           <t>Runo</t>
@@ -30692,6 +30757,11 @@
           <t>Ahmedabad</t>
         </is>
       </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Joycee Ashok Rokade</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>Runo</t>
@@ -30710,6 +30780,11 @@
       <c r="X8" t="inlineStr">
         <is>
           <t>Ahmedabad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Joycee Ashok Rokade</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
@@ -30734,6 +30809,11 @@
           <t>Surat</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Jyoti Andrews</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
           <t>Sales Diary</t>
@@ -30759,6 +30839,11 @@
           <t>Surat</t>
         </is>
       </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Jyoti Andrews</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>Sales Diary</t>
@@ -30777,6 +30862,11 @@
       <c r="X9" t="inlineStr">
         <is>
           <t>Surat</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Jyoti Andrews</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
@@ -30801,6 +30891,11 @@
           <t>Vadodara</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Kishor Mhaske</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
           <t>QR code</t>
@@ -30826,6 +30921,11 @@
           <t>Vadodara</t>
         </is>
       </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kishor Mhaske</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>QR code</t>
@@ -30844,6 +30944,11 @@
       <c r="X10" t="inlineStr">
         <is>
           <t>Vadodara</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Kishor Mhaske</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
@@ -30868,6 +30973,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Madan Kolkur</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>Walk-in</t>
@@ -30893,6 +31003,11 @@
           <t>Goa</t>
         </is>
       </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Madan Kolkur</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Walk-in</t>
@@ -30906,6 +31021,11 @@
       <c r="X11" t="inlineStr">
         <is>
           <t>Goa</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Madan Kolkur</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
@@ -30930,6 +31050,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Nilesh Khandkar</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Referral</t>
@@ -30955,6 +31080,11 @@
           <t>Bengaluru</t>
         </is>
       </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Nilesh Khandkar</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>Referral</t>
@@ -30968,6 +31098,11 @@
       <c r="X12" t="inlineStr">
         <is>
           <t>Bengaluru</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Nilesh Khandkar</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
@@ -30992,6 +31127,11 @@
           <t>Chennai</t>
         </is>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Palash Sharma</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
           <t>Field visit</t>
@@ -31017,6 +31157,11 @@
           <t>Chennai</t>
         </is>
       </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Palash Sharma</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>Field visit</t>
@@ -31030,6 +31175,11 @@
       <c r="X13" t="inlineStr">
         <is>
           <t>Chennai</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Palash Sharma</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
@@ -31054,6 +31204,11 @@
           <t>Hyderabad</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Architect</t>
@@ -31079,6 +31234,11 @@
           <t>Hyderabad</t>
         </is>
       </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>Architect</t>
@@ -31092,6 +31252,11 @@
       <c r="X14" t="inlineStr">
         <is>
           <t>Hyderabad</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Pankaj Kumar</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
@@ -31116,6 +31281,11 @@
           <t>Kochi</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Paramjeet Saini</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Existing relationship</t>
@@ -31141,6 +31311,11 @@
           <t>Kochi</t>
         </is>
       </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Paramjeet Saini</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>Existing relationship</t>
@@ -31154,6 +31329,11 @@
       <c r="X15" t="inlineStr">
         <is>
           <t>Kochi</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Paramjeet Saini</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
@@ -31178,6 +31358,11 @@
           <t>New Delhi</t>
         </is>
       </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Pradeep Yashwantrao Washimkar</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31203,6 +31388,11 @@
           <t>New Delhi</t>
         </is>
       </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Pradeep Yashwantrao Washimkar</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31216,6 +31406,11 @@
       <c r="X16" t="inlineStr">
         <is>
           <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Pradeep Yashwantrao Washimkar</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
@@ -31240,6 +31435,11 @@
           <t>Gurugram</t>
         </is>
       </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Pradnya Kaustubh Khare</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31260,6 +31460,11 @@
           <t>Gurugram</t>
         </is>
       </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Pradnya Kaustubh Khare</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31268,6 +31473,11 @@
       <c r="X17" t="inlineStr">
         <is>
           <t>Gurugram</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Pradnya Kaustubh Khare</t>
         </is>
       </c>
     </row>
@@ -31282,6 +31492,11 @@
           <t>Noida</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Pravez Khan</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr">
         <is>
           <t>Noida</t>
@@ -31292,9 +31507,19 @@
           <t>Noida</t>
         </is>
       </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Pravez Khan</t>
+        </is>
+      </c>
       <c r="X18" t="inlineStr">
         <is>
           <t>Noida</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Pravez Khan</t>
         </is>
       </c>
     </row>
@@ -31309,6 +31534,11 @@
           <t>Jaipur</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Pravin Shingare</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr">
         <is>
           <t>Jaipur</t>
@@ -31319,9 +31549,19 @@
           <t>Jaipur</t>
         </is>
       </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Pravin Shingare</t>
+        </is>
+      </c>
       <c r="X19" t="inlineStr">
         <is>
           <t>Jaipur</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Pravin Shingare</t>
         </is>
       </c>
     </row>
@@ -31336,6 +31576,11 @@
           <t>Chandigarh</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Rahul Bajpai</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr">
         <is>
           <t>Chandigarh</t>
@@ -31346,9 +31591,19 @@
           <t>Chandigarh</t>
         </is>
       </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Rahul Bajpai</t>
+        </is>
+      </c>
       <c r="X20" t="inlineStr">
         <is>
           <t>Chandigarh</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Rahul Bajpai</t>
         </is>
       </c>
     </row>
@@ -31363,6 +31618,11 @@
           <t>Lucknow</t>
         </is>
       </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Roshan Bisani</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr">
         <is>
           <t>Lucknow</t>
@@ -31373,9 +31633,19 @@
           <t>Lucknow</t>
         </is>
       </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Roshan Bisani</t>
+        </is>
+      </c>
       <c r="X21" t="inlineStr">
         <is>
           <t>Lucknow</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Roshan Bisani</t>
         </is>
       </c>
     </row>
@@ -31390,6 +31660,11 @@
           <t>Kolkata</t>
         </is>
       </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Salimullah</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr">
         <is>
           <t>Kolkata</t>
@@ -31400,9 +31675,19 @@
           <t>Kolkata</t>
         </is>
       </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Salimullah</t>
+        </is>
+      </c>
       <c r="X22" t="inlineStr">
         <is>
           <t>Kolkata</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Salimullah</t>
         </is>
       </c>
     </row>
@@ -31417,6 +31702,11 @@
           <t>Indore</t>
         </is>
       </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sanket Jage</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr">
         <is>
           <t>Indore</t>
@@ -31427,9 +31717,104 @@
           <t>Indore</t>
         </is>
       </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Sanket Jage</t>
+        </is>
+      </c>
       <c r="X23" t="inlineStr">
         <is>
           <t>Indore</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Sanket Jage</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sunil Dongrani</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sunil Dongrani</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Sunil Dongrani</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Tarun Goverkar</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Tarun Goverkar</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Tarun Goverkar</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Vijay Pandhre</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Vijay Pandhre</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Vijay Pandhre</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Virendra Pratap Ram Singh</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Virendra Pratap Ram Singh</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Virendra Pratap Ram Singh</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>ZippyScale Admin</t>
         </is>
       </c>
     </row>

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -7242,7 +7242,7 @@
       <formula1>='Dealer companies'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$H$2:$H$16</formula1>
+      <formula1>=Lists!$H$2:$H$17</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$I$2:$I$4</formula1>
@@ -18991,7 +18991,7 @@
       <formula1>=Lists!$S$2:$S$4</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$T$2:$T$16</formula1>
+      <formula1>=Lists!$T$2:$T$17</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$U$2:$U$4</formula1>
@@ -30122,7 +30122,7 @@
       <formula1>=Lists!$AB$2:$AB$28</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$AC$2:$AC$16</formula1>
+      <formula1>=Lists!$AC$2:$AC$17</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$AD$2:$AD$4</formula1>
@@ -31615,7 +31615,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field sales</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -31650,7 +31650,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field sales</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
@@ -31675,7 +31675,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Architect</t>
+          <t>Field sales</t>
         </is>
       </c>
     </row>
@@ -31707,7 +31707,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -31742,7 +31742,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
@@ -31767,7 +31767,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Existing relationship</t>
+          <t>Architect</t>
         </is>
       </c>
     </row>
@@ -31799,7 +31799,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
@@ -31859,7 +31859,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Existing relationship</t>
         </is>
       </c>
     </row>
@@ -31889,6 +31889,11 @@
           <t>Pradnya Kaustubh Khare</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31919,6 +31924,11 @@
           <t>Pradnya Kaustubh Khare</t>
         </is>
       </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
       <c r="W17" t="inlineStr">
         <is>
           <t>Other</t>
@@ -31937,6 +31947,11 @@
       <c r="AB17" t="inlineStr">
         <is>
           <t>Pradnya Kaustubh Khare</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -7224,13 +7224,13 @@
       <formula1>=Lists!$B$2:$B$17</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$C$2:$C$23</formula1>
+      <formula1>=Lists!$C$2:$C$161</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$D$2:$D$37</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type several separated by commas." type="list">
-      <formula1>=Lists!$E$2:$E$23</formula1>
+      <formula1>=Lists!$E$2:$E$161</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
       <formula1>=Lists!$F$2:$F$28</formula1>
@@ -18976,13 +18976,13 @@
       <formula1>=Lists!$N$2:$N$17</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$O$2:$O$23</formula1>
+      <formula1>=Lists!$O$2:$O$161</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$P$2:$P$37</formula1>
     </dataValidation>
     <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type several separated by commas." type="list">
-      <formula1>=Lists!$Q$2:$Q$23</formula1>
+      <formula1>=Lists!$Q$2:$Q$161</formula1>
     </dataValidation>
     <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." promptTitle="Pick or type" prompt="Pick from the list, or type it." type="list">
       <formula1>=Lists!$R$2:$R$28</formula1>
@@ -30113,7 +30113,7 @@
       <formula1>=Lists!$Y$2:$Y$10</formula1>
     </dataValidation>
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$Z$2:$Z$23</formula1>
+      <formula1>=Lists!$Z$2:$Z$161</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$AA$2:$AA$37</formula1>
@@ -30138,7 +30138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AD161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32298,26 +32298,51 @@
       </c>
     </row>
     <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Kalyan</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>Meghalaya</t>
         </is>
       </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Kalyan</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>Sunil Dongrani</t>
         </is>
       </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Kalyan</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Meghalaya</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Kalyan</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>Sunil Dongrani</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Kalyan</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>Meghalaya</t>
@@ -32330,26 +32355,51 @@
       </c>
     </row>
     <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Dombivli</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>Mizoram</t>
         </is>
       </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Dombivli</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>Tarun Goverkar</t>
         </is>
       </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Dombivli</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Mizoram</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Dombivli</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Tarun Goverkar</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>Dombivli</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>Mizoram</t>
@@ -32362,26 +32412,51 @@
       </c>
     </row>
     <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Bhiwandi</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>Nagaland</t>
         </is>
       </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Bhiwandi</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>Vijay Pandhre</t>
         </is>
       </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Bhiwandi</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Nagaland</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>Bhiwandi</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>Vijay Pandhre</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Bhiwandi</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>Nagaland</t>
@@ -32394,26 +32469,51 @@
       </c>
     </row>
     <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Vasai-Virar</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Vasai-Virar</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>Virendra Pratap Ram Singh</t>
         </is>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Vasai-Virar</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Vasai-Virar</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>Virendra Pratap Ram Singh</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>Vasai-Virar</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>Odisha</t>
@@ -32426,26 +32526,51 @@
       </c>
     </row>
     <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>Puducherry</t>
         </is>
       </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>ZippyScale Admin</t>
         </is>
       </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Puducherry</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>ZippyScale Admin</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>Panvel</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>Puducherry</t>
@@ -32458,16 +32583,41 @@
       </c>
     </row>
     <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Punjab</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>Mira-Bhayandar</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>Punjab</t>
@@ -32475,16 +32625,41 @@
       </c>
     </row>
     <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ulhasnagar</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Ulhasnagar</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Ulhasnagar</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Rajasthan</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Ulhasnagar</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>Ulhasnagar</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>Rajasthan</t>
@@ -32492,16 +32667,41 @@
       </c>
     </row>
     <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>Sikkim</t>
         </is>
       </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Sikkim</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>Pimpri-Chinchwad</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>Sikkim</t>
@@ -32509,16 +32709,41 @@
       </c>
     </row>
     <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Aurangabad</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>Tamil Nadu</t>
@@ -32526,16 +32751,41 @@
       </c>
     </row>
     <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Telangana</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>Solapur</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>Telangana</t>
@@ -32543,16 +32793,41 @@
       </c>
     </row>
     <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>Tripura</t>
         </is>
       </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Tripura</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>Kolhapur</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>Tripura</t>
@@ -32560,16 +32835,41 @@
       </c>
     </row>
     <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
         </is>
       </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>Sangli</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>Uttar Pradesh</t>
@@ -32577,16 +32877,41 @@
       </c>
     </row>
     <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
         </is>
       </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>Amravati</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>Uttarakhand</t>
@@ -32594,19 +32919,3392 @@
       </c>
     </row>
     <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>West Bengal</t>
         </is>
       </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>Akola</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>West Bengal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>Jalgaon</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>Ahmednagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>Latur</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>Nanded</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>Satara</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>Ratnagiri</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>Rajkot</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>Gandhinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>Bhavnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>Jamnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>Anand</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Vapi</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Vapi</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Vapi</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>Vapi</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>Vapi</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>Bharuch</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>Mehsana</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>Junagadh</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Gandhidham</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Gandhidham</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>Gandhidham</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>Gandhidham</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>Gandhidham</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>Panaji</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>Margao</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Mapusa</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Mapusa</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>Mapusa</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Mapusa</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>Mapusa</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>Silvassa</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>Daman</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>Mysuru</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>Mangaluru</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>Hubballi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>Belagavi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>Davanagere</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>Kalaburagi</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>Udupi</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>Coimbatore</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>Madurai</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>Tiruchirappalli</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>Salem</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>Tiruppur</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>Erode</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>Vellore</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>Tirunelveli</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>Hosur</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>Secunderabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>Warangal</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>Karimnagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>Nizamabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>Khammam</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>Visakhapatnam</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>Vijayawada</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>Guntur</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>Nellore</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>Tirupati</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>Kakinada</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>Rajahmundry</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>Kurnool</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>Anantapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>Thiruvananthapuram</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>Kozhikode</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>Thrissur</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>Kollam</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>Kannur</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>Puducherry</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>Delhi</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>Faridabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>Panipat</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>Sonipat</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>Ambala</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>Karnal</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hisar</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Hisar</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>Hisar</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>Hisar</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>Hisar</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>Rohtak</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>Ghaziabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Greater Noida</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Greater Noida</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>Greater Noida</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>Greater Noida</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>Greater Noida</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>Kanpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>Agra</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>Varanasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>Meerut</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>Prayagraj</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>Bareilly</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Aligarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Moradabad</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Gorakhpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>Jodhpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>Udaipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>Kota</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ajmer</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Ajmer</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>Ajmer</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>Ajmer</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>Ajmer</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>Bikaner</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>Ludhiana</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>Amritsar</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>Jalandhar</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>Mohali</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Patiala</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Patiala</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Patiala</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>Patiala</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>Patiala</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Bathinda</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>Dehradun</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>Haridwar</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>Haldwani</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Shimla</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>Jammu</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>Srinagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>Howrah</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>Durgapur</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>Asansol</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>Siliguri</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>Bhubaneswar</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>Cuttack</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Rourkela</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Rourkela</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>Rourkela</t>
+        </is>
+      </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>Rourkela</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>Rourkela</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>Patna</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>Gaya</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Muzaffarpur</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Muzaffarpur</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Muzaffarpur</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>Muzaffarpur</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>Muzaffarpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>Ranchi</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>Dhanbad</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bokaro</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Bokaro</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Bokaro</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>Bokaro</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>Bokaro</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>Guwahati</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>Dibrugarh</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>Silchar</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>Shillong</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>Agartala</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>Imphal</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>Gangtok</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>Bhopal</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>Jabalpur</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>Gwalior</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>Ujjain</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>Sagar</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>Raipur</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>Bhilai</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>Bilaspur</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Durg</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Durg</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Durg</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>Durg</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>Durg</t>
         </is>
       </c>
     </row>

--- a/ego/EGO-Premium-Upload-Template.xlsx
+++ b/ego/EGO-Premium-Upload-Template.xlsx
@@ -7242,7 +7242,7 @@
       <formula1>='Dealer companies'!$B$3:$B$1000</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$H$2:$H$17</formula1>
+      <formula1>=Lists!$H$2:$H$18</formula1>
     </dataValidation>
     <dataValidation sqref="U2:U1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$I$2:$I$4</formula1>
@@ -18991,7 +18991,7 @@
       <formula1>=Lists!$S$2:$S$4</formula1>
     </dataValidation>
     <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$T$2:$T$17</formula1>
+      <formula1>=Lists!$T$2:$T$18</formula1>
     </dataValidation>
     <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$U$2:$U$4</formula1>
@@ -30122,7 +30122,7 @@
       <formula1>=Lists!$AB$2:$AB$28</formula1>
     </dataValidation>
     <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
-      <formula1>=Lists!$AC$2:$AC$17</formula1>
+      <formula1>=Lists!$AC$2:$AC$18</formula1>
     </dataValidation>
     <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not in the list" error="Choose a value from the dropdown." type="list">
       <formula1>=Lists!$AD$2:$AD$4</formula1>
@@ -31976,6 +31976,11 @@
           <t>Pravez Khan</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr">
         <is>
           <t>Noida</t>
@@ -31996,6 +32001,11 @@
           <t>Pravez Khan</t>
         </is>
       </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
+        </is>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
           <t>Noida</t>
@@ -32009,6 +32019,11 @@
       <c r="AB18" t="inlineStr">
         <is>
           <t>Pravez Khan</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Exhibition</t>
         </is>
       </c>
     </row>
